--- a/output/yearly_total_coral_cover_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_25_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.276651397406591</v>
+        <v>1.260629274873283</v>
       </c>
       <c r="C3" t="n">
-        <v>4.579800898743207</v>
+        <v>4.627042598271563</v>
       </c>
       <c r="D3" t="n">
-        <v>6.206800520985303</v>
+        <v>6.061590218050157</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0632528171351</v>
+        <v>11.949262091195</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.438011611958163</v>
+        <v>1.404416117057677</v>
       </c>
       <c r="C4" t="n">
-        <v>4.983381227085814</v>
+        <v>5.110050472756745</v>
       </c>
       <c r="D4" t="n">
-        <v>6.551755858957144</v>
+        <v>6.274335892278483</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97314869800112</v>
+        <v>12.7888024820929</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.651351490710088</v>
+        <v>1.60806479038684</v>
       </c>
       <c r="C5" t="n">
-        <v>5.494703862573759</v>
+        <v>5.721081659839967</v>
       </c>
       <c r="D5" t="n">
-        <v>6.909072785906234</v>
+        <v>6.49212681545015</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05512813919008</v>
+        <v>13.82127326567696</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.892213569762657</v>
+        <v>1.842596124192255</v>
       </c>
       <c r="C6" t="n">
-        <v>6.132818652496884</v>
+        <v>6.494633441921318</v>
       </c>
       <c r="D6" t="n">
-        <v>7.314816327797777</v>
+        <v>6.786285747106966</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33984855005732</v>
+        <v>15.12351531322054</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.179105151935558</v>
+        <v>2.098908940457975</v>
       </c>
       <c r="C7" t="n">
-        <v>6.90060384531452</v>
+        <v>7.405891854586793</v>
       </c>
       <c r="D7" t="n">
-        <v>7.707681028632708</v>
+        <v>7.032728582467112</v>
       </c>
       <c r="E7" t="n">
-        <v>16.78739002588279</v>
+        <v>16.53752937751188</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.406744323228631</v>
+        <v>1.323023300763625</v>
       </c>
       <c r="C8" t="n">
-        <v>4.599022903691279</v>
+        <v>5.098519569639781</v>
       </c>
       <c r="D8" t="n">
-        <v>5.923407908376139</v>
+        <v>5.294899507897396</v>
       </c>
       <c r="E8" t="n">
-        <v>11.92917513529605</v>
+        <v>11.7164423783008</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.803890779012079</v>
+        <v>1.674638163518097</v>
       </c>
       <c r="C9" t="n">
-        <v>5.570560288025962</v>
+        <v>6.301053583176933</v>
       </c>
       <c r="D9" t="n">
-        <v>6.500525639413402</v>
+        <v>5.714017932747256</v>
       </c>
       <c r="E9" t="n">
-        <v>13.87497670645144</v>
+        <v>13.68970967944229</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.231730115287882</v>
+        <v>2.051228950791209</v>
       </c>
       <c r="C10" t="n">
-        <v>6.677324884944246</v>
+        <v>7.659810102534892</v>
       </c>
       <c r="D10" t="n">
-        <v>7.043750334373437</v>
+        <v>6.17884972861833</v>
       </c>
       <c r="E10" t="n">
-        <v>15.95280533460556</v>
+        <v>15.88988878194443</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.671333310131128</v>
+        <v>2.425376648118073</v>
       </c>
       <c r="C11" t="n">
-        <v>7.918342691383081</v>
+        <v>9.094489608210596</v>
       </c>
       <c r="D11" t="n">
-        <v>7.594640967296202</v>
+        <v>6.635575706554214</v>
       </c>
       <c r="E11" t="n">
-        <v>18.18431696881041</v>
+        <v>18.15544196288288</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.116052237855871</v>
+        <v>2.804136291038854</v>
       </c>
       <c r="C12" t="n">
-        <v>9.325622466932423</v>
+        <v>10.59674858430539</v>
       </c>
       <c r="D12" t="n">
-        <v>8.081260242294892</v>
+        <v>7.024770244693031</v>
       </c>
       <c r="E12" t="n">
-        <v>20.52293494708319</v>
+        <v>20.42565512003727</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.540069909478629</v>
+        <v>3.169366304965615</v>
       </c>
       <c r="C13" t="n">
-        <v>10.84528486243403</v>
+        <v>12.10898429994513</v>
       </c>
       <c r="D13" t="n">
-        <v>8.641283896921813</v>
+        <v>7.461518183855962</v>
       </c>
       <c r="E13" t="n">
-        <v>23.02663866883447</v>
+        <v>22.73986878876671</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.028310391927995</v>
+        <v>1.826708500860913</v>
       </c>
       <c r="C14" t="n">
-        <v>7.734866185018218</v>
+        <v>8.451365294531625</v>
       </c>
       <c r="D14" t="n">
-        <v>6.512541205845727</v>
+        <v>5.710600593631719</v>
       </c>
       <c r="E14" t="n">
-        <v>16.27571778279194</v>
+        <v>15.98867438902426</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.101489865802552</v>
+        <v>1.873086262409532</v>
       </c>
       <c r="C15" t="n">
-        <v>8.498940788279425</v>
+        <v>9.04554845757292</v>
       </c>
       <c r="D15" t="n">
-        <v>6.54891495828807</v>
+        <v>5.678831237922293</v>
       </c>
       <c r="E15" t="n">
-        <v>17.14934561237005</v>
+        <v>16.59746595790475</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.458139171801334</v>
+        <v>2.189680262075044</v>
       </c>
       <c r="C16" t="n">
-        <v>10.23084191334122</v>
+        <v>10.5974068711529</v>
       </c>
       <c r="D16" t="n">
-        <v>7.100951692386052</v>
+        <v>6.128726940870435</v>
       </c>
       <c r="E16" t="n">
-        <v>19.78993277752861</v>
+        <v>18.91581407409837</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.978211806580281</v>
+        <v>1.763091249625719</v>
       </c>
       <c r="C17" t="n">
-        <v>9.668339748715971</v>
+        <v>9.684548403313087</v>
       </c>
       <c r="D17" t="n">
-        <v>6.61430917286795</v>
+        <v>5.67806547471298</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2608607281642</v>
+        <v>17.12570512765179</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.26687508405997</v>
+        <v>2.03302278090838</v>
       </c>
       <c r="C18" t="n">
-        <v>11.43244219847707</v>
+        <v>11.20447056407391</v>
       </c>
       <c r="D18" t="n">
-        <v>7.040515303712618</v>
+        <v>6.088985793802525</v>
       </c>
       <c r="E18" t="n">
-        <v>20.73983258624965</v>
+        <v>19.32647913878482</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.280491924717873</v>
+        <v>2.063614039372711</v>
       </c>
       <c r="C19" t="n">
-        <v>12.38453130457858</v>
+        <v>11.87987371468755</v>
       </c>
       <c r="D19" t="n">
-        <v>7.144050416602487</v>
+        <v>6.184303678407848</v>
       </c>
       <c r="E19" t="n">
-        <v>21.80907364589894</v>
+        <v>20.12779143246811</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.540193644922282</v>
+        <v>2.331758789833642</v>
       </c>
       <c r="C20" t="n">
-        <v>14.39077200811511</v>
+        <v>13.58912592021237</v>
       </c>
       <c r="D20" t="n">
-        <v>7.556757516513761</v>
+        <v>6.594114622591595</v>
       </c>
       <c r="E20" t="n">
-        <v>24.48772316955115</v>
+        <v>22.51499933263761</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.510791907111332</v>
+        <v>1.406746285415255</v>
       </c>
       <c r="C21" t="n">
-        <v>10.70553656329864</v>
+        <v>9.934462098906154</v>
       </c>
       <c r="D21" t="n">
-        <v>6.290676042162991</v>
+        <v>5.500192425657543</v>
       </c>
       <c r="E21" t="n">
-        <v>18.50700451257297</v>
+        <v>16.84140080997895</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_25_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.260629274873283</v>
+        <v>1.283474543951106</v>
       </c>
       <c r="C3" t="n">
-        <v>4.627042598271563</v>
+        <v>4.616390635680486</v>
       </c>
       <c r="D3" t="n">
-        <v>6.061590218050157</v>
+        <v>6.012640277516411</v>
       </c>
       <c r="E3" t="n">
-        <v>11.949262091195</v>
+        <v>11.912505457148</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.404416117057677</v>
+        <v>1.454226501332875</v>
       </c>
       <c r="C4" t="n">
-        <v>5.110050472756745</v>
+        <v>5.102681199081394</v>
       </c>
       <c r="D4" t="n">
-        <v>6.274335892278483</v>
+        <v>6.219731828878717</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7888024820929</v>
+        <v>12.77663952929299</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.60806479038684</v>
+        <v>1.676786881827862</v>
       </c>
       <c r="C5" t="n">
-        <v>5.721081659839967</v>
+        <v>5.737638227159069</v>
       </c>
       <c r="D5" t="n">
-        <v>6.49212681545015</v>
+        <v>6.414305689591514</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82127326567696</v>
+        <v>13.82873079857845</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.842596124192255</v>
+        <v>1.922332686345479</v>
       </c>
       <c r="C6" t="n">
-        <v>6.494633441921318</v>
+        <v>6.503964827383629</v>
       </c>
       <c r="D6" t="n">
-        <v>6.786285747106966</v>
+        <v>6.638270295065077</v>
       </c>
       <c r="E6" t="n">
-        <v>15.12351531322054</v>
+        <v>15.06456780879418</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.098908940457975</v>
+        <v>2.190704218296536</v>
       </c>
       <c r="C7" t="n">
-        <v>7.405891854586793</v>
+        <v>7.441325962413651</v>
       </c>
       <c r="D7" t="n">
-        <v>7.032728582467112</v>
+        <v>6.897834821834392</v>
       </c>
       <c r="E7" t="n">
-        <v>16.53752937751188</v>
+        <v>16.52986500254458</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.323023300763625</v>
+        <v>1.382251255677152</v>
       </c>
       <c r="C8" t="n">
-        <v>5.098519569639781</v>
+        <v>5.120427571667927</v>
       </c>
       <c r="D8" t="n">
-        <v>5.294899507897396</v>
+        <v>5.038336262914554</v>
       </c>
       <c r="E8" t="n">
-        <v>11.7164423783008</v>
+        <v>11.54101509025963</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.674638163518097</v>
+        <v>1.766869354427141</v>
       </c>
       <c r="C9" t="n">
-        <v>6.301053583176933</v>
+        <v>6.372526932690883</v>
       </c>
       <c r="D9" t="n">
-        <v>5.714017932747256</v>
+        <v>5.399203527182757</v>
       </c>
       <c r="E9" t="n">
-        <v>13.68970967944229</v>
+        <v>13.53859981430078</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.051228950791209</v>
+        <v>2.172003549361327</v>
       </c>
       <c r="C10" t="n">
-        <v>7.659810102534892</v>
+        <v>7.864357190641979</v>
       </c>
       <c r="D10" t="n">
-        <v>6.17884972861833</v>
+        <v>5.80400863365353</v>
       </c>
       <c r="E10" t="n">
-        <v>15.88988878194443</v>
+        <v>15.84036937365684</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.425376648118073</v>
+        <v>2.579751493783311</v>
       </c>
       <c r="C11" t="n">
-        <v>9.094489608210596</v>
+        <v>9.516627343496104</v>
       </c>
       <c r="D11" t="n">
-        <v>6.635575706554214</v>
+        <v>6.210783824895795</v>
       </c>
       <c r="E11" t="n">
-        <v>18.15544196288288</v>
+        <v>18.30716266217521</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.804136291038854</v>
+        <v>3.003758426569163</v>
       </c>
       <c r="C12" t="n">
-        <v>10.59674858430539</v>
+        <v>11.25091913040869</v>
       </c>
       <c r="D12" t="n">
-        <v>7.024770244693031</v>
+        <v>6.572755730866709</v>
       </c>
       <c r="E12" t="n">
-        <v>20.42565512003727</v>
+        <v>20.82743328784456</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.169366304965615</v>
+        <v>3.413088126376763</v>
       </c>
       <c r="C13" t="n">
-        <v>12.10898429994513</v>
+        <v>13.08409710311753</v>
       </c>
       <c r="D13" t="n">
-        <v>7.461518183855962</v>
+        <v>6.9682234764219</v>
       </c>
       <c r="E13" t="n">
-        <v>22.73986878876671</v>
+        <v>23.4654087059162</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.826708500860913</v>
+        <v>1.974196458469911</v>
       </c>
       <c r="C14" t="n">
-        <v>8.451365294531625</v>
+        <v>9.133581774212733</v>
       </c>
       <c r="D14" t="n">
-        <v>5.710600593631719</v>
+        <v>5.34632310797094</v>
       </c>
       <c r="E14" t="n">
-        <v>15.98867438902426</v>
+        <v>16.45410134065358</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.873086262409532</v>
+        <v>2.038481298143992</v>
       </c>
       <c r="C15" t="n">
-        <v>9.04554845757292</v>
+        <v>10.04396623783784</v>
       </c>
       <c r="D15" t="n">
-        <v>5.678831237922293</v>
+        <v>5.285405662922426</v>
       </c>
       <c r="E15" t="n">
-        <v>16.59746595790475</v>
+        <v>17.36785319890426</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.189680262075044</v>
+        <v>2.378774687390022</v>
       </c>
       <c r="C16" t="n">
-        <v>10.5974068711529</v>
+        <v>12.03906410493117</v>
       </c>
       <c r="D16" t="n">
-        <v>6.128726940870435</v>
+        <v>5.681531044108972</v>
       </c>
       <c r="E16" t="n">
-        <v>18.91581407409837</v>
+        <v>20.09936983643016</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.763091249625719</v>
+        <v>1.909469832328919</v>
       </c>
       <c r="C17" t="n">
-        <v>9.684548403313087</v>
+        <v>11.2477656378312</v>
       </c>
       <c r="D17" t="n">
-        <v>5.67806547471298</v>
+        <v>5.214425303905381</v>
       </c>
       <c r="E17" t="n">
-        <v>17.12570512765179</v>
+        <v>18.3716607740655</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.03302278090838</v>
+        <v>2.179420998565665</v>
       </c>
       <c r="C18" t="n">
-        <v>11.20447056407391</v>
+        <v>13.25384926173504</v>
       </c>
       <c r="D18" t="n">
-        <v>6.088985793802525</v>
+        <v>5.584092584462476</v>
       </c>
       <c r="E18" t="n">
-        <v>19.32647913878482</v>
+        <v>21.01736284476318</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.063614039372711</v>
+        <v>2.181227414341479</v>
       </c>
       <c r="C19" t="n">
-        <v>11.87987371468755</v>
+        <v>14.29508105938217</v>
       </c>
       <c r="D19" t="n">
-        <v>6.184303678407848</v>
+        <v>5.62767236505399</v>
       </c>
       <c r="E19" t="n">
-        <v>20.12779143246811</v>
+        <v>22.10398083877764</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.331758789833642</v>
+        <v>2.416522886618312</v>
       </c>
       <c r="C20" t="n">
-        <v>13.58912592021237</v>
+        <v>16.5427826107782</v>
       </c>
       <c r="D20" t="n">
-        <v>6.594114622591595</v>
+        <v>5.931925796077119</v>
       </c>
       <c r="E20" t="n">
-        <v>22.51499933263761</v>
+        <v>24.89123129347363</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.406746285415255</v>
+        <v>1.429944983666607</v>
       </c>
       <c r="C21" t="n">
-        <v>9.934462098906154</v>
+        <v>12.2110859376693</v>
       </c>
       <c r="D21" t="n">
-        <v>5.500192425657543</v>
+        <v>4.92384761840241</v>
       </c>
       <c r="E21" t="n">
-        <v>16.84140080997895</v>
+        <v>18.56487853973831</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_25_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.283474543951106</v>
+        <v>2.615817192463943</v>
       </c>
       <c r="C3" t="n">
-        <v>4.616390635680486</v>
+        <v>7.891236128707156</v>
       </c>
       <c r="D3" t="n">
-        <v>6.012640277516411</v>
+        <v>8.15925388766745</v>
       </c>
       <c r="E3" t="n">
-        <v>11.912505457148</v>
+        <v>18.66630720883855</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.454226501332875</v>
+        <v>1.120254104948468</v>
       </c>
       <c r="C4" t="n">
-        <v>5.102681199081394</v>
+        <v>4.954767599826057</v>
       </c>
       <c r="D4" t="n">
-        <v>6.219731828878717</v>
+        <v>5.719876896079014</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77663952929299</v>
+        <v>11.79489860085354</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.676786881827862</v>
+        <v>1.244512064640947</v>
       </c>
       <c r="C5" t="n">
-        <v>5.737638227159069</v>
+        <v>6.135002118039823</v>
       </c>
       <c r="D5" t="n">
-        <v>6.414305689591514</v>
+        <v>6.012469484184061</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82873079857845</v>
+        <v>13.39198366686483</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.922332686345479</v>
+        <v>1.367809231654729</v>
       </c>
       <c r="C6" t="n">
-        <v>6.503964827383629</v>
+        <v>7.596900009026303</v>
       </c>
       <c r="D6" t="n">
-        <v>6.638270295065077</v>
+        <v>6.320028505638779</v>
       </c>
       <c r="E6" t="n">
-        <v>15.06456780879418</v>
+        <v>15.28473774631981</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.190704218296536</v>
+        <v>1.497456805954622</v>
       </c>
       <c r="C7" t="n">
-        <v>7.441325962413651</v>
+        <v>9.269440171861056</v>
       </c>
       <c r="D7" t="n">
-        <v>6.897834821834392</v>
+        <v>6.64236741426295</v>
       </c>
       <c r="E7" t="n">
-        <v>16.52986500254458</v>
+        <v>17.40926439207863</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.382251255677152</v>
+        <v>1.626359894628358</v>
       </c>
       <c r="C8" t="n">
-        <v>5.120427571667927</v>
+        <v>11.0783509683588</v>
       </c>
       <c r="D8" t="n">
-        <v>5.038336262914554</v>
+        <v>7.032739023838256</v>
       </c>
       <c r="E8" t="n">
-        <v>11.54101509025963</v>
+        <v>19.73744988682541</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.766869354427141</v>
+        <v>1.731316798062692</v>
       </c>
       <c r="C9" t="n">
-        <v>6.372526932690883</v>
+        <v>13.01865996231476</v>
       </c>
       <c r="D9" t="n">
-        <v>5.399203527182757</v>
+        <v>7.43921624386673</v>
       </c>
       <c r="E9" t="n">
-        <v>13.53859981430078</v>
+        <v>22.18919300424418</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.172003549361327</v>
+        <v>1.070635141389317</v>
       </c>
       <c r="C10" t="n">
-        <v>7.864357190641979</v>
+        <v>9.127190596658087</v>
       </c>
       <c r="D10" t="n">
-        <v>5.80400863365353</v>
+        <v>5.841555919901201</v>
       </c>
       <c r="E10" t="n">
-        <v>15.84036937365684</v>
+        <v>16.03938165794861</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.579751493783311</v>
+        <v>0.9940784554121503</v>
       </c>
       <c r="C11" t="n">
-        <v>9.516627343496104</v>
+        <v>10.12578509150977</v>
       </c>
       <c r="D11" t="n">
-        <v>6.210783824895795</v>
+        <v>5.671831376791013</v>
       </c>
       <c r="E11" t="n">
-        <v>18.30716266217521</v>
+        <v>16.79169492371294</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.003758426569163</v>
+        <v>1.053857073123739</v>
       </c>
       <c r="C12" t="n">
-        <v>11.25091913040869</v>
+        <v>12.16511069267942</v>
       </c>
       <c r="D12" t="n">
-        <v>6.572755730866709</v>
+        <v>5.977763596388404</v>
       </c>
       <c r="E12" t="n">
-        <v>20.82743328784456</v>
+        <v>19.19673136219156</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.413088126376763</v>
+        <v>0.8219388129495147</v>
       </c>
       <c r="C13" t="n">
-        <v>13.08409710311753</v>
+        <v>11.61757036306689</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9682234764219</v>
+        <v>5.411471885624759</v>
       </c>
       <c r="E13" t="n">
-        <v>23.4654087059162</v>
+        <v>17.85098106164116</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.974196458469911</v>
+        <v>0.8754244278768809</v>
       </c>
       <c r="C14" t="n">
-        <v>9.133581774212733</v>
+        <v>13.66335586413047</v>
       </c>
       <c r="D14" t="n">
-        <v>5.34632310797094</v>
+        <v>5.688599627579547</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45410134065358</v>
+        <v>20.2273799195869</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.038481298143992</v>
+        <v>0.8331307367779284</v>
       </c>
       <c r="C15" t="n">
-        <v>10.04396623783784</v>
+        <v>14.73839905271186</v>
       </c>
       <c r="D15" t="n">
-        <v>5.285405662922426</v>
+        <v>5.667060082948372</v>
       </c>
       <c r="E15" t="n">
-        <v>17.36785319890426</v>
+        <v>21.23858987243816</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.378774687390022</v>
+        <v>0.8917803446296326</v>
       </c>
       <c r="C16" t="n">
-        <v>12.03906410493117</v>
+        <v>17.01695693445237</v>
       </c>
       <c r="D16" t="n">
-        <v>5.681531044108972</v>
+        <v>5.97834282753391</v>
       </c>
       <c r="E16" t="n">
-        <v>20.09936983643016</v>
+        <v>23.88708010661591</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.909469832328919</v>
+        <v>0.526167682091078</v>
       </c>
       <c r="C17" t="n">
-        <v>11.2477656378312</v>
+        <v>12.46377797926538</v>
       </c>
       <c r="D17" t="n">
-        <v>5.214425303905381</v>
+        <v>4.939722478780081</v>
       </c>
       <c r="E17" t="n">
-        <v>18.3716607740655</v>
+        <v>17.92966814013654</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.179420998565665</v>
+        <v>0.4115682725743479</v>
       </c>
       <c r="C18" t="n">
-        <v>13.25384926173504</v>
+        <v>11.24223839825629</v>
       </c>
       <c r="D18" t="n">
-        <v>5.584092584462476</v>
+        <v>4.445491049508153</v>
       </c>
       <c r="E18" t="n">
-        <v>21.01736284476318</v>
+        <v>16.09929772033879</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.181227414341479</v>
+        <v>0.4741645061971246</v>
       </c>
       <c r="C19" t="n">
-        <v>14.29508105938217</v>
+        <v>13.8228015087772</v>
       </c>
       <c r="D19" t="n">
-        <v>5.62767236505399</v>
+        <v>4.8650114784869</v>
       </c>
       <c r="E19" t="n">
-        <v>22.10398083877764</v>
+        <v>19.16197749346122</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.416522886618312</v>
+        <v>0.5303499273111696</v>
       </c>
       <c r="C20" t="n">
-        <v>16.5427826107782</v>
+        <v>16.4432628459987</v>
       </c>
       <c r="D20" t="n">
-        <v>5.931925796077119</v>
+        <v>5.247402209291033</v>
       </c>
       <c r="E20" t="n">
-        <v>24.89123129347363</v>
+        <v>22.2210149826009</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.429944983666607</v>
+        <v>0.5770320306481053</v>
       </c>
       <c r="C21" t="n">
-        <v>12.2110859376693</v>
+        <v>19.00961024976212</v>
       </c>
       <c r="D21" t="n">
-        <v>4.92384761840241</v>
+        <v>5.582492335704553</v>
       </c>
       <c r="E21" t="n">
-        <v>18.56487853973831</v>
+        <v>25.16913461611477</v>
       </c>
     </row>
   </sheetData>
